--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Cash_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Cash_Template.xlsx
@@ -10,7 +10,7 @@
     <sheet name="借支单" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">借支单!$A$1:$I$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">借支单!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
     <t>借支日期：</t>
   </si>
   <si>
-    <t>{advanceDate}</t>
+    <t>{advanceDateStr}</t>
   </si>
   <si>
     <t>部门：</t>
@@ -74,7 +74,7 @@
     <t>归还时限</t>
   </si>
   <si>
-    <t>{backDate}</t>
+    <t>{backDateStr}</t>
   </si>
   <si>
     <t>借支金额（元）</t>
@@ -147,14 +147,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -935,7 +934,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -965,22 +964,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1004,7 +1003,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1601,7 +1600,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.875" customWidth="1"/>
-    <col min="2" max="2" width="23.375" customWidth="1"/>
+    <col min="2" max="2" width="31.3666666666667" customWidth="1"/>
     <col min="3" max="3" width="17.25" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="28.375" customWidth="1"/>
@@ -1910,7 +1909,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="47" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Cash_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Cash_Template.xlsx
@@ -10,7 +10,7 @@
     <sheet name="借支单" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">借支单!$A$1:$I$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">借支单!$A$1:$I$17,借支单!$N$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
